--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BBB836-4E62-1248-AF2E-67EBB855005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1FEE61-D6C1-0D43-A16E-FE6E3163E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="700" yWindow="3440" windowWidth="22660" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="164">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1953,6 +1953,22 @@
   </si>
   <si>
     <t>사역마용 실키 퍼프</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ResourceKey</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>stick01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>stick02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>stick03</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3025,54 +3041,69 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61CC70E-C5FC-CC4C-B7A4-2DD0D72CDAD8}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="27.33203125" customWidth="1"/>
     <col min="2" max="2" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="15">
+      <c r="C2" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15">
       <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="15">
+      <c r="C3" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15">
       <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="15">
+      <c r="C4" s="10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15">
       <c r="A5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="15">
+      <c r="C5" s="10" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15">
       <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
@@ -3080,7 +3111,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15">
+    <row r="7" spans="1:3" ht="15">
       <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
@@ -3088,7 +3119,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15">
+    <row r="8" spans="1:3" ht="15">
       <c r="A8" s="7" t="s">
         <v>52</v>
       </c>
@@ -3096,7 +3127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15">
+    <row r="9" spans="1:3" ht="15">
       <c r="A9" s="7" t="s">
         <v>53</v>
       </c>
@@ -3104,7 +3135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15">
+    <row r="10" spans="1:3" ht="15">
       <c r="A10" s="7" t="s">
         <v>73</v>
       </c>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1FEE61-D6C1-0D43-A16E-FE6E3163E5DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9229AB-4E8A-C94F-8BDD-2E3D7BD288E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="700" yWindow="3440" windowWidth="22660" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1964,11 +1964,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>stick02</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>stick03</t>
+    <t>powder01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bubblegun01</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9229AB-4E8A-C94F-8BDD-2E3D7BD288E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05555A33-9928-EA42-A26C-A45F508C97A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="3440" windowWidth="22660" windowHeight="13740" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="233">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1729,26 +1729,6 @@
     <t>Material</t>
   </si>
   <si>
-    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1969,6 +1949,1314 @@
   </si>
   <si>
     <t>bubblegun01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
+  </si>
+  <si>
+    <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
+  </si>
+  <si>
+    <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
+  </si>
+  <si>
+    <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하늘색_실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파란색_실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하늘색 실타래</t>
+  </si>
+  <si>
+    <t>파란색 실타래</t>
+  </si>
+  <si>
+    <t>초록색 실타래</t>
+  </si>
+  <si>
+    <t>노란색 실타래</t>
+  </si>
+  <si>
+    <t>주황색 실타래</t>
+  </si>
+  <si>
+    <t>분홍색 실타래</t>
+  </si>
+  <si>
+    <t>보라색 실타래</t>
+  </si>
+  <si>
+    <t>무지개 실타래</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노란색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주황색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>분홍색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보라색_실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무지개</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+  </si>
+  <si>
+    <t>icon_yarn_ball_skyblue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_blue</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>초록색_실타래]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_green</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_yellow</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_orange</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_pink</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_purple</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_yarn_ball_rainbow</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>포시즌스 별자리 이불</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이불</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>포시즌스_별자리이불]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_four_seasons_constellation_blanket</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노르망디 구스 깃털 한 가닥</t>
+  </si>
+  <si>
+    <t>페킨 덕 깃털 한 가닥</t>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깃털</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노르망디구스]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>깃털</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페킨덕]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2차 가공 재료. 노르망디 거위에게서 얻은 하늘하늘한 깃털 한 가닥. 오리의 깃털보다 길고 부드럽다.
+이걸 얻는데 </t>
+  </si>
+  <si>
+    <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
+  </si>
+  <si>
+    <t>icon_normandy_goose_feather</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_pekin_duck_feather</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>문라이트 인 헤븐 이불</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이불_문라이트인헤븐이불]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_moonlight_in_heaven_blanket</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>이불</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>머니캐쳐누빔이불]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>머니캐쳐 누빔 이불</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_money_catcher_quilted_blanket</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>라벤더 문 필로우</t>
+  </si>
+  <si>
+    <t>노르망디 바디필로우</t>
+  </si>
+  <si>
+    <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플레이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>라벤더문필로우]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>플레이어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노르망디바디필로우]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_lavender_moon_pillow</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_normandy_body_pillow</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtfactRateUp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확률보정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>굿나잇아이마스크]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>확률보정</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>폭닥폭닥 수면양말]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>굿나잇 아이마스크</t>
+  </si>
+  <si>
+    <r>
+      <t>폭닥폭닥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수면양말</t>
+    </r>
+  </si>
+  <si>
+    <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
+  </si>
+  <si>
+    <r>
+      <t>체온을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>높여주는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>폭닥폭닥한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수면양말로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>마도구</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>합성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>성공</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>확률을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>프로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>높여준다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>한바탕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>춤을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>춰도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>미끄러지지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>않도록</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>내장된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>발바닥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>패드는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>덤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하루에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다섯</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>켤레까지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>겹쳐서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>착용할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>있다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?!</t>
+    </r>
+  </si>
+  <si>
+    <t>icon_goodnight_eye_mask</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>icon_cozy_sleep_socks</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1979,7 +3267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2043,6 +3331,14 @@
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2127,7 +3423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2155,6 +3451,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2373,7 +3675,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
@@ -2429,10 +3731,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>5</v>
@@ -2449,10 +3751,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>16</v>
@@ -2469,10 +3771,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>109</v>
+        <v>160</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>15</v>
@@ -2489,10 +3791,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>110</v>
+        <v>161</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>22</v>
@@ -2511,8 +3813,8 @@
       <c r="B7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>111</v>
+      <c r="C7" s="21" t="s">
+        <v>162</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>21</v>
@@ -2531,8 +3833,8 @@
       <c r="B8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>112</v>
+      <c r="C8" s="21" t="s">
+        <v>163</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>23</v>
@@ -2552,7 +3854,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -2572,7 +3874,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>55</v>
@@ -2592,7 +3894,7 @@
         <v>74</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>75</v>
@@ -2609,10 +3911,10 @@
         <v>35</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>39</v>
@@ -2629,10 +3931,10 @@
         <v>36</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>40</v>
@@ -2649,10 +3951,10 @@
         <v>37</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>41</v>
@@ -2669,10 +3971,10 @@
         <v>38</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>42</v>
@@ -2690,10 +3992,10 @@
         <v>86</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>95</v>
@@ -2713,7 +4015,7 @@
         <v>80</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>96</v>
@@ -2730,10 +4032,10 @@
         <v>88</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>97</v>
@@ -2750,10 +4052,10 @@
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>64</v>
@@ -2767,16 +4069,16 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>107</v>
@@ -2787,250 +4089,583 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>57</v>
+        <v>164</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>135</v>
+        <v>179</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>66</v>
+        <v>187</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>67</v>
+        <v>188</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>67</v>
+        <v>190</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>67</v>
+        <v>191</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>81</v>
+        <v>175</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>65</v>
+        <v>192</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>58</v>
+        <v>176</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>83</v>
+        <v>193</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>85</v>
+        <v>177</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>83</v>
+        <v>194</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E28" s="10" t="s">
-        <v>83</v>
+        <v>195</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F28">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>90</v>
+        <v>197</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>83</v>
+        <v>199</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>129</v>
+        <v>208</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>84</v>
+        <v>211</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>100</v>
+        <v>212</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>99</v>
+        <v>213</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>98</v>
+        <v>215</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>107</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F32">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A33" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A34" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A36" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A37" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A38" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A39" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A40" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A41" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A43" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A44" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A45" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A46" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A47" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B47" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="10" t="s">
+      <c r="C47" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D47" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E47" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F32">
+      <c r="F47">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A33" s="7"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="20"/>
+    <row r="48" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A48" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A49" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>224</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3067,7 +4702,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15">
@@ -3078,7 +4713,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15">
@@ -3089,7 +4724,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15">
@@ -3100,7 +4735,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15">
@@ -3304,8 +4939,12 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
+      <c r="A12" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hansu/lunaria-data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05555A33-9928-EA42-A26C-A45F508C97A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB4CC3-A62C-4649-A8DA-58B4ED70FB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="234">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2718,6 +2718,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2746,6 +2747,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2766,6 +2768,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2786,6 +2789,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2806,6 +2810,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">, </t>
@@ -2826,6 +2831,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2846,6 +2852,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2866,6 +2873,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2886,6 +2894,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> 5</t>
@@ -2906,6 +2915,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2926,6 +2936,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
@@ -2946,6 +2957,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2966,6 +2978,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2986,6 +2999,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3006,6 +3020,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3026,6 +3041,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3046,6 +3062,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3066,6 +3083,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3086,6 +3104,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3106,6 +3125,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">. </t>
@@ -3126,6 +3146,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3146,6 +3167,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3166,6 +3188,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3186,6 +3209,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3206,6 +3230,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3226,6 +3251,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3246,6 +3272,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>?!</t>
@@ -3257,6 +3284,10 @@
   </si>
   <si>
     <t>icon_cozy_sleep_socks</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ArtifactRateUp</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3423,7 +3454,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3455,7 +3486,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -4337,7 +4367,7 @@
       <c r="C33" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="10" t="s">
         <v>207</v>
       </c>
       <c r="E33" s="20" t="s">
@@ -4377,7 +4407,7 @@
       <c r="C35" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="10" t="s">
         <v>222</v>
       </c>
       <c r="E35" s="10" t="s">
@@ -4397,7 +4427,7 @@
       <c r="C36" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="10" t="s">
         <v>223</v>
       </c>
       <c r="E36" s="10" t="s">
@@ -4640,8 +4670,8 @@
       <c r="D48" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="23" t="s">
-        <v>224</v>
+      <c r="E48" s="10" t="s">
+        <v>233</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4651,17 +4681,17 @@
       <c r="A49" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="23" t="s">
         <v>230</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="E49" s="23" t="s">
-        <v>224</v>
+      <c r="E49" s="10" t="s">
+        <v>233</v>
       </c>
       <c r="F49">
         <v>2</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB4CC3-A62C-4649-A8DA-58B4ED70FB81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB47279-312C-3942-96D0-FFEF8D95C3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="233">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2592,10 +2592,6 @@
   </si>
   <si>
     <t>icon_normandy_body_pillow</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArtfactRateUp</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -4659,19 +4655,19 @@
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4679,19 +4675,19 @@
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D49" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="E49" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="F49">
         <v>2</v>
@@ -4970,7 +4966,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="10" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>47</v>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB47279-312C-3942-96D0-FFEF8D95C3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4B8F22-C06D-6548-9D5B-8C6839F60BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
-    <sheet name="Artifact" sheetId="3" r:id="rId2"/>
-    <sheet name="InitialItem" sheetId="2" r:id="rId3"/>
-    <sheet name="InventoryTab" sheetId="4" r:id="rId4"/>
+    <sheet name="InventoryTab" sheetId="4" r:id="rId2"/>
+    <sheet name="Artifact" sheetId="3" r:id="rId3"/>
+    <sheet name="InitialItem" sheetId="2" r:id="rId4"/>
+    <sheet name="FamiliarCall" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="251">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1615,50 +1616,6 @@
   </si>
   <si>
     <t>페로페로 향수</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>페로페로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>향수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>]</t>
-    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -3284,6 +3241,530 @@
   </si>
   <si>
     <t>ArtifactRateUp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_A형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_B형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_C형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_A형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_B형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>페로페로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>향수_C형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar03</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노말B형</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>노말C형</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarId</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>노말</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>_C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>형</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>]</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>hp</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3294,7 +3775,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3367,8 +3848,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3411,6 +3906,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEF2CD"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3450,7 +3951,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -3483,6 +3984,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3701,12 +4205,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="32" style="3" customWidth="1"/>
     <col min="2" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="87" customWidth="1"/>
+    <col min="3" max="3" width="106" customWidth="1"/>
     <col min="4" max="4" width="30.83203125" customWidth="1"/>
     <col min="5" max="5" width="18.83203125" style="11" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" customWidth="1"/>
@@ -3757,10 +4261,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>5</v>
@@ -3777,10 +4281,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>16</v>
@@ -3797,10 +4301,10 @@
         <v>13</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>15</v>
@@ -3817,10 +4321,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>22</v>
@@ -3840,7 +4344,7 @@
         <v>19</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>21</v>
@@ -3860,7 +4364,7 @@
         <v>20</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>23</v>
@@ -3880,7 +4384,7 @@
         <v>50</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
@@ -3900,7 +4404,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>55</v>
@@ -3920,7 +4424,7 @@
         <v>74</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>75</v>
@@ -3937,10 +4441,10 @@
         <v>35</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>39</v>
@@ -3957,16 +4461,16 @@
         <v>36</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>40</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F13">
         <v>2</v>
@@ -3977,16 +4481,16 @@
         <v>37</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F14">
         <v>3</v>
@@ -3997,16 +4501,16 @@
         <v>38</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F15">
         <v>4</v>
@@ -4018,16 +4522,16 @@
         <v>86</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>95</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F16">
         <v>5</v>
@@ -4041,13 +4545,13 @@
         <v>80</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>96</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F17">
         <v>6</v>
@@ -4058,16 +4562,16 @@
         <v>88</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>97</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F18">
         <v>7</v>
@@ -4078,16 +4582,16 @@
         <v>59</v>
       </c>
       <c r="B19" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>144</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>145</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>64</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F19">
         <v>8</v>
@@ -4095,19 +4599,19 @@
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="C20" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>133</v>
-      </c>
       <c r="E20" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -4115,19 +4619,19 @@
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F21">
         <v>10</v>
@@ -4135,19 +4639,19 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F22">
         <v>11</v>
@@ -4155,19 +4659,19 @@
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1">
       <c r="A23" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>190</v>
-      </c>
       <c r="E23" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F23">
         <v>12</v>
@@ -4175,19 +4679,19 @@
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24">
         <v>13</v>
@@ -4195,19 +4699,19 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F25">
         <v>14</v>
@@ -4215,19 +4719,19 @@
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F26">
         <v>15</v>
@@ -4235,19 +4739,19 @@
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F27">
         <v>16</v>
@@ -4255,19 +4759,19 @@
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28">
         <v>17</v>
@@ -4275,19 +4779,19 @@
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1">
       <c r="A29" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="D29" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="10" t="s">
-        <v>199</v>
-      </c>
       <c r="E29" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F29">
         <v>18</v>
@@ -4295,19 +4799,19 @@
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B30" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="D30" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D30" s="10" t="s">
-        <v>211</v>
-      </c>
       <c r="E30" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F30">
         <v>19</v>
@@ -4315,19 +4819,19 @@
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
       <c r="A31" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="B31" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="C31" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="D31" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D31" s="10" t="s">
-        <v>215</v>
-      </c>
       <c r="E31" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F31">
         <v>20</v>
@@ -4335,19 +4839,19 @@
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F32">
         <v>21</v>
@@ -4355,19 +4859,19 @@
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F33">
         <v>22</v>
@@ -4378,10 +4882,10 @@
         <v>57</v>
       </c>
       <c r="B34" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C34" s="14" t="s">
         <v>129</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>130</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>61</v>
@@ -4395,16 +4899,16 @@
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>66</v>
@@ -4415,16 +4919,16 @@
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>66</v>
@@ -4441,7 +4945,7 @@
         <v>56</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>62</v>
@@ -4458,10 +4962,10 @@
         <v>76</v>
       </c>
       <c r="B38" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C38" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>153</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>78</v>
@@ -4478,10 +4982,10 @@
         <v>77</v>
       </c>
       <c r="B39" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>79</v>
@@ -4498,10 +5002,10 @@
         <v>81</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>82</v>
@@ -4518,10 +5022,10 @@
         <v>58</v>
       </c>
       <c r="B41" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="14" t="s">
         <v>142</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>143</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>63</v>
@@ -4541,10 +5045,10 @@
         <v>92</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>83</v>
@@ -4558,13 +5062,13 @@
         <v>89</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>83</v>
@@ -4578,10 +5082,10 @@
         <v>90</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>94</v>
@@ -4598,10 +5102,10 @@
         <v>91</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>93</v>
@@ -4615,16 +5119,16 @@
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="B46" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E46" s="17" t="s">
         <v>98</v>
@@ -4635,61 +5139,101 @@
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>106</v>
+        <v>233</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>228</v>
+        <v>110</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="E48" s="10" t="s">
-        <v>232</v>
+        <v>100</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>98</v>
       </c>
       <c r="F48">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1">
       <c r="A49" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A50" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="B50" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="B49" s="23" t="s">
+      <c r="C50" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="D50" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="E50" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E49" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="F49">
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A51" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F51">
         <v>2</v>
       </c>
     </row>
@@ -4701,6 +5245,120 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="10"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61CC70E-C5FC-CC4C-B7A4-2DD0D72CDAD8}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
@@ -4728,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15">
@@ -4739,7 +5397,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15">
@@ -4750,7 +5408,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15">
@@ -4761,7 +5419,7 @@
         <v>32</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15">
@@ -4810,7 +5468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3404EB02-A5A0-8544-AC1C-24A6932127D0}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
@@ -4864,112 +5522,99 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{086B8DAC-B633-AD4E-BA75-289E4BADB1B2}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE7BAC6-87E0-6847-8CF9-31160B85BD77}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22.5" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="1" max="2" width="18.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="10" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>24</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="10" t="s">
-        <v>7</v>
+        <v>238</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="10"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>47</v>
+        <v>246</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15">
+      <c r="A3" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15">
+      <c r="A4" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15">
+      <c r="A5" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>245</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4B8F22-C06D-6548-9D5B-8C6839F60BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF84383-E9E5-AE44-A9EB-2EA9FA36D7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3600" yWindow="660" windowWidth="25800" windowHeight="16540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -3764,7 +3764,7 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>hp</t>
+    <t>MaxHp</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>

--- a/excel/ItemData.xlsx
+++ b/excel/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF84383-E9E5-AE44-A9EB-2EA9FA36D7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95A0863F-80AB-8141-9B8E-59F1A436BD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3600" yWindow="660" windowWidth="25800" windowHeight="16540" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="253">
   <si>
     <t>string</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3765,6 +3765,14 @@
   </si>
   <si>
     <t>MaxHp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsTemporary</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5524,7 +5532,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AE7BAC6-87E0-6847-8CF9-31160B85BD77}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="2" width="18.6640625" customWidth="1"/>
@@ -5532,7 +5540,7 @@
     <col min="4" max="4" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
@@ -5548,8 +5556,11 @@
       <c r="E1" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="10" t="s">
         <v>238</v>
       </c>
@@ -5565,8 +5576,11 @@
       <c r="E2" s="10" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="15">
+      <c r="F2" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="24" t="s">
         <v>235</v>
       </c>
@@ -5582,8 +5596,11 @@
       <c r="E3">
         <v>100</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="15">
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="24" t="s">
         <v>236</v>
       </c>
@@ -5599,8 +5616,11 @@
       <c r="E4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15">
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="24" t="s">
         <v>237</v>
       </c>
@@ -5615,6 +5635,9 @@
       </c>
       <c r="E5">
         <v>100</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
